--- a/workers/sync/fixtures/rc_out/workbooks/rc_out_edge.xlsx
+++ b/workers/sync/fixtures/rc_out/workbooks/rc_out_edge.xlsx
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>9999</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="5">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9999</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="13">
